--- a/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
+++ b/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_pi3x_spatial/MindCube/SPAgent_4B_pi3x_spatial_MindCube.xlsx
@@ -1800,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>11.63490056991577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>7.975518465042114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1858,7 +1858,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>20.24281430244446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>15.94112133979797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1916,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>8.485865592956543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1945,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>6.513633251190186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1974,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>8.092424392700195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>16.59667253494263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -2032,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>13.68928551673889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>9.1343674659729</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2090,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>5.602574586868286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2119,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>7.204480171203613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>9.893677949905396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>6.832757949829102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>12.41114187240601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>20.61771988868713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>7.557990550994873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>6.548009157180786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>12.19729709625244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>11.24600410461426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2380,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>6.539400339126587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>13.50868582725525</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>11.5790696144104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>11.33076453208923</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>8.901817560195923</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>13.13655161857605</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>12.99479031562805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -2583,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>14.13414239883423</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>15.49136710166931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>5.760339498519897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>5.321767330169678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -2699,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>17.65057468414307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>7.549957275390625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>6.192657947540283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -2786,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>6.288109302520752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>8.542855262756348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>7.938128471374512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>7.157404899597168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>9.326850891113281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>18.83420062065125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>6.852245330810547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="I43">
-        <v>5.478480339050293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -3018,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>7.312690258026123</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>7.801327705383301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>17.09341955184937</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>11.56145524978638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>7.59062123298645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>4.276282787322998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>10.46132302284241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>32.68729376792908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -3250,7 +3250,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>8.863240480422974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>4.939774513244629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -3308,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>5.908358573913574</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>10.01641941070557</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -3366,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>8.854426860809326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -3395,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>11.54228186607361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>14.56336903572083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>11.90616035461426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -3482,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>4.815663576126099</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -3511,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>6.271183252334595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>14.34293389320374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>7.983695507049561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -3598,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>4.996545314788818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>8.518923044204712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -3656,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>12.6402313709259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>15.77852463722229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -3714,7 +3714,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <v>12.85644054412842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -3743,7 +3743,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>13.32032227516174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>7.209253311157227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>11.67134761810303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -3830,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>12.66445016860962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>10.56071972846985</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>5.381204843521118</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -3917,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>31.06662154197693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -3946,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>15.71422386169434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -3975,7 +3975,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>16.7445387840271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>7.271371364593506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>6.73559045791626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>12.35199642181396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -4091,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>20.08410215377808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -4120,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>5.124199151992798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>4.858975172042847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -4178,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>18.58158469200134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>5.022625684738159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -4236,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>12.13674688339233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -4265,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>6.676445960998535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>5.359408378601074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4323,7 +4323,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>11.57428288459778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4352,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>13.50857996940613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>6.680964231491089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>15.44501900672913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>6.269491195678711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4468,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <v>13.03529024124146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -4497,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>6.037523031234741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>4.05759072303772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -4555,7 +4555,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>13.76915621757507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -4584,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>8.220497131347656</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -4613,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>7.074084043502808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -4642,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>10.28781604766846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -4671,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>5.371211528778076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -4700,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>7.967326879501343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>21.67754077911377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -4758,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>8.163118600845337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -4787,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>7.826940536499023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>18.61854457855225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>7.660248041152954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>8.133800268173218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>4.217314004898071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>8.723220586776733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4961,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>11.61946558952332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>18.49557042121887</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -5019,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>15.85693001747131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>28.12222218513489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -5077,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="I115">
-        <v>5.007154226303101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>6.438094139099121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -5135,7 +5135,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>13.93935203552246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>14.07937908172607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -5193,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>5.308243989944458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -5222,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>6.734843492507935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>10.24913930892944</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
